--- a/prediction_log.xlsx
+++ b/prediction_log.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pivot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raw_Submission_Log'!$A$1:$K$533</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raw_Submission_Log'!$A$1:$K$543</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <pivotCaches>
@@ -7861,7 +7861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q533"/>
+  <dimension ref="A1:Q543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="11.9375" customWidth="1" style="6" min="2" max="2"/>
@@ -39446,8 +39446,378 @@
         </is>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>20260621</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>5002</v>
+      </c>
+      <c r="F534" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G534" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="H534" t="n">
+        <v>0.4608203269744834</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>20260622</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>키움</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>10001</v>
+      </c>
+      <c r="F535" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G535" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="H535" t="n">
+        <v>0.4504230667407982</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>20260623</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>9002</v>
+      </c>
+      <c r="F536" t="n">
+        <v>7002</v>
+      </c>
+      <c r="G536" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="H536" t="n">
+        <v>0.4310526763820235</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>20260624</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>12001</v>
+      </c>
+      <c r="F537" t="n">
+        <v>6002</v>
+      </c>
+      <c r="G537" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="H537" t="n">
+        <v>0.526987038886179</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>20260625</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>롯데</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>2002</v>
+      </c>
+      <c r="F538" t="n">
+        <v>3001</v>
+      </c>
+      <c r="G538" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H538" t="n">
+        <v>0.4079630087989528</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>20260626</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>5002</v>
+      </c>
+      <c r="F539" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G539" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="H539" t="n">
+        <v>0.5383655784780842</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>20260627</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>키움</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>10001</v>
+      </c>
+      <c r="F540" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G540" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="H540" t="n">
+        <v>0.4306675780791778</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>20260628</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>SSG</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>9002</v>
+      </c>
+      <c r="F541" t="n">
+        <v>7002</v>
+      </c>
+      <c r="G541" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="H541" t="n">
+        <v>0.8037014358127266</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>20260629</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>12001</v>
+      </c>
+      <c r="F542" t="n">
+        <v>6002</v>
+      </c>
+      <c r="G542" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="H542" t="n">
+        <v>0.6471805678578536</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>20260630</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>롯데</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>2002</v>
+      </c>
+      <c r="F543" t="n">
+        <v>3001</v>
+      </c>
+      <c r="G543" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="H543" t="n">
+        <v>0.445677836074832</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>elo_sp_l2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K533"/>
+  <autoFilter ref="A1:K543"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
